--- a/reports/play_character_adapter.xlsx
+++ b/reports/play_character_adapter.xlsx
@@ -36,10 +36,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Speaker_Target_Evidence'!$A$1:$I$317</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Relationship_Candidate_Summary'!$A$1:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Excluded_Low_Quality_Evidence'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Methodology_Notes'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Methodology_Notes'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Corpus_Documented_Relations'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Tara_Annotation_Evidence'!$A$1:$K$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Semantic_Relation_Edges'!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Semantic_Relation_Edges'!$A$1:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Graph_Export_Index'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2136,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2263,8 +2263,20 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tara relationship graph</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TARA_FULL_ANNOTATION_V4 Target_Relation values are retained in Tara_Annotation_Evidence only. They are not converted to pairwise social-relation edges because their field semantics do not establish a relationship between the utterance speaker and target.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11266,7 +11278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11527,1133 +11539,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bharati</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TARA_S0403</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Don’t tell me about your father. He is more worried about your career than hers.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bharati</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>TARA_S0408</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>It’s time Tara decided what she wants to be. Women have to do that as well these days. She must have a career.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bharati</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TARA_S0403</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Don’t tell me about your father. He is more worried about your career than hers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FATHER_CHILD</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TARA_S0815</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>If daddy wants to stop her from saying something to us, maybe it’s not good for us to hear it.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FATHER_SON</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TARA_S0060; TARA_S0454; TARA_S0456; TARA_S0458; TARA_S0460; TARA_S0464; TARA_S0466; TARA_S0472; TARA_S0480; TARA_S0779</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>I haven't decided yet. (Looks at Patel.) I might stay back in the cave and do my jigsaw puzzle. || Mummy’s knitting and I’m helping her sort out her mistake.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Roopa</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>TARA_S0688; TARA_S0717</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>You led me on! || Yes. Please stay.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FATHER_DAUGHTER</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TARA_S0054</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>We'll both come with you.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>TARA_S0049; TARA_S0404; TARA_S0409; TARA_S0411; TARA_S0416; TARA_S0428; TARA_S0430; TARA_S0476; TARA_S0478; TARA_S0570</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>You can take Tara. She'll make a great business woman. || That’s because I’m more sure of what I want. She is just . . . playing it cool.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>TARA_S0086; TARA_S0534; TARA_S0874</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No! No! That won't do. I can't have all that just swimming in my mind. The mind wanders too much. Unnecessary details, irrelevant characters which do not figure anywhere. I've got to put it all down. I've got to make a s || I was looking through this old scrap book. A present daddy gave me just before left. It’s got all our news cuttings. Dr Thakkar is in the headlines. Then there are interviews with my mom and dad. And worst of all a hideo</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bharati</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUSBAND_WIFE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>TARA_S0328; TARA_S0346; TARA_S0350; TARA_S0465; TARA_S0490; TARA_S0492; TARA_S0494; TARA_S0496; TARA_S0498; TARA_S0500</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>You will have to obey me. It’s my turn now. || (pushes her down). Sit down. Now listen. I am going to fix an appointment for you and you are going to see that doctor.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FATHER_SON</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>TARA_S0046; TARA_S0053; TARA_S0055; TARA_S0455; TARA_S0457; TARA_S0461; TARA_S0463; TARA_S0488; TARA_S0586</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>I was just thinking . . . It may be a good idea for you to come to the office with me. (Glances surreptitiously towards the kitchen.) || (firmly). Chandan, I think I must insist that you come.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OTHER_MALE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>TARA_S0469; TARA_S0477</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>But you can think of turning him into a sissy—teaching him to knit! || You will not. I won’t allow it.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>TARA_S0594</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Do me a favour. Both of you. Don’t ever go there. Just lock it up. Or better still, burn the whole place down! (Exits to his bedroom.)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FATHER_DAUGHTER</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>TARA_S0065; TARA_S0841</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(to Chandan). Well, take care. If you two need to go out anywhere, just call the office. I’ll send the car. (Pats Tara.) Take care. || Don’t ever go there without my permission.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OTHER_FAMILY</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>TARA_S0590</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Nothing.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>TARA_S0845; TARA_S0849</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Never. || You will not!</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>TARA_S0055; TARA_S0594</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>No! || Do me a favour. Both of you. Don’t ever go there. Just lock it up. Or better still, burn the whole place down! (Exits to his bedroom.)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Roopa</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bharati</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HUSBAND_WIFE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>TARA_S0868</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>All right. Stay inside! We’re going to get a present for you! (Exits.)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Roopa</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OTHER_MALE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TARA_S0871</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(shouting). There. At least you are not blind! Do you get the message? Freaks. hand. Tara turns away from him. Chandan is crushed.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Roopa</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>TARA_S0653; TARA_S0655; TARA_S0659; TARA_S0665; TARA_S0671; TARA_S0687; TARA_S0691; TARA_S0697; TARA_S0706; TARA_S0708</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>A boy definitely! || Yes. It’s bad enough studying in an all-girls’ school. I would definitely want a boyfriend.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OTHER_MALE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>TARA_S0122</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>We women mature fast. Speaking of maturity, you better not skip any physiotherapy sessions. Daddy wants you to be big and sturdy. He will find out from the hospital and. .. This music is so. . . I don’t know.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>TARA_S0700</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Rapist.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chandan</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SIBLINGS</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>TARA_S0002; TARA_S0438; TARA_S0602; TARA_S0604; TARA_S0606; TARA_S0614; TARA_S0765</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>And me. Maybe we still are. Like we’ve always been. Inseparable. The way we started in life. Two lives and one body, in one comfortable womb. Till we were forced out... And separated. It is obvious Tara is winning. Bhara || A little bit, I suppose. But he has always been so . . . He has never really asked for much. He is so happy with so little. I have always demanded more and more.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>FATHER_DAUGHTER</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>6</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>TARA_S0765; TARA_S0778; TARA_S0784; TARA_S0800; TARA_S0816; TARA_S0819A</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Yes! We do. We do! And we are more sensitive, more intelligent, more compassionate human beings than creeps like you and... and... || Daddy.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Tara</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Roopa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>RELATIONAL</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TARA_UTTERANCE_ANNOTATION</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>TARA_S0737; TARA_S0739; TARA_S0741</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>So how does it feel having one tit smaller than the other? Don’t worry—it’s not very noticeable, except from a certain angle. Then it’s very noticeable. || I’d sooner be one-eyed, one-armed and one-legged than be an imbecile like you. An imbecile with uneven tits.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Existing utterance-level annotation mapped to known character endpoints; review source QA and context.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I31"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12752,10 +11639,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/reports/play_character_adapter.xlsx
+++ b/reports/play_character_adapter.xlsx
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Methodology_Notes'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Corpus_Documented_Relations'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Tara_Annotation_Evidence'!$A$1:$K$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Semantic_Relation_Edges'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Semantic_Relation_Edges'!$A$1:$I$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Graph_Export_Index'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11278,7 +11278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11539,8 +11539,1133 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bharati</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TARA_S0403</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Don’t tell me about your father. He is more worried about your career than hers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bharati</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TARA_S0408</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>It’s time Tara decided what she wants to be. Women have to do that as well these days. She must have a career.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bharati</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TARA_S0403</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Don’t tell me about your father. He is more worried about your career than hers.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FATHER_CHILD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TARA_S0815</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>If daddy wants to stop her from saying something to us, maybe it’s not good for us to hear it.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FATHER_SON</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TARA_S0060; TARA_S0454; TARA_S0456; TARA_S0458; TARA_S0460; TARA_S0464; TARA_S0466; TARA_S0472; TARA_S0480; TARA_S0779</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>I haven't decided yet. (Looks at Patel.) I might stay back in the cave and do my jigsaw puzzle. || Mummy’s knitting and I’m helping her sort out her mistake.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Roopa</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TARA_S0688; TARA_S0717</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>You led me on! || Yes. Please stay.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FATHER_DAUGHTER</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TARA_S0054</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>We'll both come with you.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TARA_S0049; TARA_S0404; TARA_S0409; TARA_S0411; TARA_S0416; TARA_S0428; TARA_S0430; TARA_S0476; TARA_S0478; TARA_S0570</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>You can take Tara. She'll make a great business woman. || That’s because I’m more sure of what I want. She is just . . . playing it cool.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TARA_S0086; TARA_S0534; TARA_S0874</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No! No! That won't do. I can't have all that just swimming in my mind. The mind wanders too much. Unnecessary details, irrelevant characters which do not figure anywhere. I've got to put it all down. I've got to make a s || I was looking through this old scrap book. A present daddy gave me just before left. It’s got all our news cuttings. Dr Thakkar is in the headlines. Then there are interviews with my mom and dad. And worst of all a hideo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bharati</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUSBAND_WIFE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TARA_S0328; TARA_S0346; TARA_S0350; TARA_S0465; TARA_S0490; TARA_S0492; TARA_S0494; TARA_S0496; TARA_S0498; TARA_S0500</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>You will have to obey me. It’s my turn now. || (pushes her down). Sit down. Now listen. I am going to fix an appointment for you and you are going to see that doctor.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FATHER_SON</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>TARA_S0046; TARA_S0053; TARA_S0055; TARA_S0455; TARA_S0457; TARA_S0461; TARA_S0463; TARA_S0488; TARA_S0586</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>I was just thinking . . . It may be a good idea for you to come to the office with me. (Glances surreptitiously towards the kitchen.) || (firmly). Chandan, I think I must insist that you come.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OTHER_MALE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>TARA_S0469; TARA_S0477</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>But you can think of turning him into a sissy—teaching him to knit! || You will not. I won’t allow it.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TARA_S0594</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Do me a favour. Both of you. Don’t ever go there. Just lock it up. Or better still, burn the whole place down! (Exits to his bedroom.)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FATHER_DAUGHTER</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TARA_S0065; TARA_S0841</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(to Chandan). Well, take care. If you two need to go out anywhere, just call the office. I’ll send the car. (Pats Tara.) Take care. || Don’t ever go there without my permission.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OTHER_FAMILY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TARA_S0590</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TARA_S0845; TARA_S0849</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Never. || You will not!</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TARA_S0055; TARA_S0594</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No! || Do me a favour. Both of you. Don’t ever go there. Just lock it up. Or better still, burn the whole place down! (Exits to his bedroom.)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Roopa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bharati</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUSBAND_WIFE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TARA_S0868</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>All right. Stay inside! We’re going to get a present for you! (Exits.)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Roopa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OTHER_MALE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TARA_S0871</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(shouting). There. At least you are not blind! Do you get the message? Freaks. hand. Tara turns away from him. Chandan is crushed.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Roopa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TARA_S0653; TARA_S0655; TARA_S0659; TARA_S0665; TARA_S0671; TARA_S0687; TARA_S0691; TARA_S0697; TARA_S0706; TARA_S0708</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>A boy definitely! || Yes. It’s bad enough studying in an all-girls’ school. I would definitely want a boyfriend.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OTHER_MALE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>TARA_S0122</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>We women mature fast. Speaking of maturity, you better not skip any physiotherapy sessions. Daddy wants you to be big and sturdy. He will find out from the hospital and. .. This music is so. . . I don’t know.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>TARA_S0700</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Rapist.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SIBLINGS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>TARA_S0002; TARA_S0438; TARA_S0602; TARA_S0604; TARA_S0606; TARA_S0614; TARA_S0765</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>And me. Maybe we still are. Like we’ve always been. Inseparable. The way we started in life. Two lives and one body, in one comfortable womb. Till we were forced out... And separated. It is obvious Tara is winning. Bhara || A little bit, I suppose. But he has always been so . . . He has never really asked for much. He is so happy with so little. I have always demanded more and more.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FATHER_DAUGHTER</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>TARA_S0765; TARA_S0778; TARA_S0784; TARA_S0800; TARA_S0816; TARA_S0819A</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Yes! We do. We do! And we are more sensitive, more intelligent, more compassionate human beings than creeps like you and... and... || Daddy.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Roopa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RELATIONAL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TARA_ANNOTATION_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>TARA_S0737; TARA_S0739; TARA_S0741</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>So how does it feel having one tit smaller than the other? Don’t worry—it’s not very noticeable, except from a certain angle. Then it’s very noticeable. || I’d sooner be one-eyed, one-armed and one-legged than be an imbecile like you. An imbecile with uneven tits.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Existing utterance-level annotation only; not independently verified as a social relationship.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11639,14 +12764,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Existing utterance annotations; not independently verified</t>
+          <t>Existing utterance annotation evidence; conflicting labels may coexist; not independently verified</t>
         </is>
       </c>
     </row>
